--- a/resultado.xlsx
+++ b/resultado.xlsx
@@ -9,7 +9,7 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cañerías" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Nodos" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Componentes Especiales" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Componentes y Fluido" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -457,19 +457,21 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="62" customWidth="1" min="10" max="10"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="9" customWidth="1" min="5" max="5"/>
+    <col width="13" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="34" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="11" max="11"/>
+    <col width="65" customWidth="1" min="12" max="12"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">
@@ -510,17 +512,27 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>Material</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Rugosidad (mm)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Nodo Inicio</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Nodo Fin</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Fittings / Válvulas</t>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fittings</t>
         </is>
       </c>
     </row>
@@ -552,15 +564,23 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
           <t>Tank 1</t>
         </is>
       </c>
-      <c r="I2" s="2" t="inlineStr">
+      <c r="K2" s="2" t="inlineStr">
         <is>
           <t>Centrifugal Pump 1</t>
         </is>
       </c>
-      <c r="J2" s="3" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>Ball (Le/D=3.0); Reducer - Contraction (100 mm)</t>
         </is>
@@ -594,15 +614,23 @@
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J3" s="4" t="inlineStr">
+        <is>
           <t>Node 1</t>
         </is>
       </c>
-      <c r="I3" s="4" t="inlineStr">
+      <c r="K3" s="4" t="inlineStr">
         <is>
           <t>Node 2</t>
         </is>
       </c>
-      <c r="J3" s="5" t="inlineStr">
+      <c r="L3" s="5" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 45° (Le/D=15.0); Mitre Bend @ 45° (Le/D=15.0)</t>
         </is>
@@ -632,19 +660,27 @@
         <v>12.744</v>
       </c>
       <c r="G4" s="2" t="n">
-        <v>2.0109</v>
+        <v>2.7713</v>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>Centrifugal Pump 1</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>Fixed dP Device 1</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>Swing Check - Vertical (Le/D=50.0); Ball (Le/D=3.0); Ball (Le/D=3.0); Reducer - Enlargement (100 mm); Ball (Le/D=3.0); Reducer - Contraction (100 mm); Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 90° (Le/D=60.0)</t>
         </is>
@@ -674,19 +710,27 @@
         <v>7.56</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.674</v>
+        <v>0.9288999999999999</v>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J5" s="4" t="inlineStr">
+        <is>
           <t>Fixed dP Device 1</t>
         </is>
       </c>
-      <c r="I5" s="4" t="inlineStr">
+      <c r="K5" s="4" t="inlineStr">
         <is>
           <t>Node 1</t>
         </is>
       </c>
-      <c r="J5" s="5" t="inlineStr">
+      <c r="L5" s="5" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0)</t>
         </is>
@@ -720,15 +764,23 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>Node 2</t>
         </is>
       </c>
-      <c r="I6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>Node 11</t>
         </is>
       </c>
-      <c r="J6" s="3" t="inlineStr">
+      <c r="L6" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -762,15 +814,23 @@
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J7" s="4" t="inlineStr">
+        <is>
           <t>Node 11</t>
         </is>
       </c>
-      <c r="I7" s="4" t="inlineStr">
+      <c r="K7" s="4" t="inlineStr">
         <is>
           <t>Node 3</t>
         </is>
       </c>
-      <c r="J7" s="5" t="inlineStr">
+      <c r="L7" s="5" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 90° (Le/D=60.0)</t>
         </is>
@@ -800,19 +860,27 @@
         <v>97.30800000000001</v>
       </c>
       <c r="G8" s="2" t="n">
-        <v>1.3481</v>
+        <v>1.8578</v>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>Node 12</t>
         </is>
       </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>Node 4</t>
         </is>
       </c>
-      <c r="J8" s="3" t="inlineStr">
+      <c r="L8" s="3" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 90° (Le/D=60.0)</t>
         </is>
@@ -846,15 +914,23 @@
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
           <t>Node 3</t>
         </is>
       </c>
-      <c r="I9" s="4" t="inlineStr">
+      <c r="K9" s="4" t="inlineStr">
         <is>
           <t>Node 12</t>
         </is>
       </c>
-      <c r="J9" s="5" t="inlineStr">
+      <c r="L9" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -888,15 +964,23 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>Node 4</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>Node 14</t>
         </is>
       </c>
-      <c r="J10" s="3" t="inlineStr">
+      <c r="L10" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -926,19 +1010,27 @@
         <v>43.2</v>
       </c>
       <c r="G11" s="4" t="n">
-        <v>1.3481</v>
+        <v>1.8578</v>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
           <t>Node 14</t>
         </is>
       </c>
-      <c r="I11" s="4" t="inlineStr">
+      <c r="K11" s="4" t="inlineStr">
         <is>
           <t>Node 5</t>
         </is>
       </c>
-      <c r="J11" s="5" t="inlineStr">
+      <c r="L11" s="5" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 90° (Le/D=60.0)</t>
         </is>
@@ -972,15 +1064,23 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>Node 5</t>
         </is>
       </c>
-      <c r="I12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>Node 16</t>
         </is>
       </c>
-      <c r="J12" s="3" t="inlineStr">
+      <c r="L12" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1010,19 +1110,27 @@
         <v>93.312</v>
       </c>
       <c r="G13" s="4" t="n">
-        <v>1.3481</v>
+        <v>1.8578</v>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
           <t>Node 16</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="K13" s="4" t="inlineStr">
         <is>
           <t>Node 6</t>
         </is>
       </c>
-      <c r="J13" s="5" t="inlineStr">
+      <c r="L13" s="5" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 90° (Le/D=60.0)</t>
         </is>
@@ -1056,15 +1164,23 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>Node 6</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>Node 18</t>
         </is>
       </c>
-      <c r="J14" s="3" t="inlineStr">
+      <c r="L14" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1094,19 +1210,27 @@
         <v>9.4068</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>1.3481</v>
+        <v>1.8578</v>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
           <t>Node 18</t>
         </is>
       </c>
-      <c r="I15" s="4" t="inlineStr">
+      <c r="K15" s="4" t="inlineStr">
         <is>
           <t>Node 7</t>
         </is>
       </c>
-      <c r="J15" s="5" t="inlineStr">
+      <c r="L15" s="5" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 90° (Le/D=60.0)</t>
         </is>
@@ -1140,15 +1264,23 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>Node 7</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>Node 19</t>
         </is>
       </c>
-      <c r="J16" s="3" t="inlineStr">
+      <c r="L16" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1178,19 +1310,27 @@
         <v>106.92</v>
       </c>
       <c r="G17" s="4" t="n">
-        <v>1.3481</v>
+        <v>1.8578</v>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
           <t>Node 19</t>
         </is>
       </c>
-      <c r="I17" s="4" t="inlineStr">
+      <c r="K17" s="4" t="inlineStr">
         <is>
           <t>Node 20</t>
         </is>
       </c>
-      <c r="J17" s="5" t="inlineStr">
+      <c r="L17" s="5" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 90° (Le/D=60.0)</t>
         </is>
@@ -1220,19 +1360,27 @@
         <v>1.8641</v>
       </c>
       <c r="G18" s="2" t="n">
-        <v>0.5617</v>
+        <v>0.7741</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>Node 20</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>Node 21</t>
         </is>
       </c>
-      <c r="J18" s="3" t="inlineStr">
+      <c r="L18" s="3" t="inlineStr">
         <is>
           <t>Mitre Bend @ 60° (Le/D=25.0); Mitre Bend @ 60° (Le/D=25.0)</t>
         </is>
@@ -1266,15 +1414,23 @@
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
           <t>Node 21</t>
         </is>
       </c>
-      <c r="I19" s="4" t="inlineStr">
+      <c r="K19" s="4" t="inlineStr">
         <is>
           <t>Node 22</t>
         </is>
       </c>
-      <c r="J19" s="5" t="inlineStr">
+      <c r="L19" s="5" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1304,19 +1460,27 @@
         <v>2.6136</v>
       </c>
       <c r="G20" s="2" t="n">
-        <v>1.3481</v>
+        <v>1.8578</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>Node 22</t>
         </is>
       </c>
-      <c r="I20" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Node 23</t>
         </is>
       </c>
-      <c r="J20" s="3" t="inlineStr">
+      <c r="L20" s="3" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 90° (Le/D=60.0)</t>
         </is>
@@ -1346,19 +1510,27 @@
         <v>0.675</v>
       </c>
       <c r="G21" s="4" t="n">
-        <v>0.5617</v>
+        <v>0.7741</v>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J21" s="4" t="inlineStr">
+        <is>
           <t>Node 23</t>
         </is>
       </c>
-      <c r="I21" s="4" t="inlineStr">
+      <c r="K21" s="4" t="inlineStr">
         <is>
           <t>Node 24</t>
         </is>
       </c>
-      <c r="J21" s="5" t="inlineStr">
+      <c r="L21" s="5" t="inlineStr">
         <is>
           <t>Mitre Bend @ 60° (Le/D=25.0); Mitre Bend @ 60° (Le/D=25.0)</t>
         </is>
@@ -1392,15 +1564,23 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
+          <t>HDPE (ISO 4427) SDR-17.0</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>Node 24</t>
         </is>
       </c>
-      <c r="I22" s="2" t="inlineStr">
+      <c r="K22" s="2" t="inlineStr">
         <is>
           <t>Node 25</t>
         </is>
       </c>
-      <c r="J22" s="3" t="inlineStr">
+      <c r="L22" s="3" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -1430,19 +1610,27 @@
         <v>2.7108</v>
       </c>
       <c r="G23" s="4" t="n">
-        <v>0.6575</v>
+        <v>0.8853</v>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
+          <t>Stainless Steel ASME B36.19M 10S</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>0.04572</v>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
           <t>Node 25</t>
         </is>
       </c>
-      <c r="I23" s="4" t="inlineStr">
+      <c r="K23" s="4" t="inlineStr">
         <is>
           <t>Node 26</t>
         </is>
       </c>
-      <c r="J23" s="5" t="inlineStr">
+      <c r="L23" s="5" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0); Reducer - Contraction (160 mm)</t>
         </is>
@@ -1472,19 +1660,27 @@
         <v>4.86</v>
       </c>
       <c r="G24" s="2" t="n">
-        <v>1.315</v>
+        <v>1.7706</v>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
+          <t>Stainless Steel ASME B36.19M 10S</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>0.04572</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>Node 26</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
         <is>
           <t>Node 27</t>
         </is>
       </c>
-      <c r="J24" s="3" t="inlineStr">
+      <c r="L24" s="3" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 90° (Le/D=60.0)</t>
         </is>
@@ -1514,19 +1710,27 @@
         <v>0.864</v>
       </c>
       <c r="G25" s="4" t="n">
-        <v>1.315</v>
+        <v>1.7706</v>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
+          <t>Stainless Steel ASME B36.19M 10S</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>0.04572</v>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
           <t>Node 27</t>
         </is>
       </c>
-      <c r="I25" s="4" t="inlineStr">
+      <c r="K25" s="4" t="inlineStr">
         <is>
           <t>Control Valve 1</t>
         </is>
       </c>
-      <c r="J25" s="5" t="inlineStr">
+      <c r="L25" s="5" t="inlineStr">
         <is>
           <t>Mitre Bend @ 90° (Le/D=60.0); Mitre Bend @ 90° (Le/D=60.0)</t>
         </is>
@@ -1560,15 +1764,23 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
+          <t>Stainless Steel ASME B36.19M 10S</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0.04572</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>Control Valve 1</t>
         </is>
       </c>
-      <c r="I26" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
         <is>
           <t>Node 29</t>
         </is>
       </c>
-      <c r="J26" s="3" t="inlineStr">
+      <c r="L26" s="3" t="inlineStr">
         <is>
           <t>Ball (Le/D=3.0); Reducer - Contraction (110 mm); Reducer - Enlargement (110 mm); Butterfly (Le/D=45.0)</t>
         </is>
@@ -1602,15 +1814,23 @@
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
+          <t>Stainless Steel ASME B36.19M 10S</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>0.04572</v>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
           <t>Node 29</t>
         </is>
       </c>
-      <c r="I27" s="4" t="inlineStr">
+      <c r="K27" s="4" t="inlineStr">
         <is>
           <t>Pressure Boundary 1</t>
         </is>
       </c>
-      <c r="J27" s="5" t="inlineStr">
+      <c r="L27" s="5" t="inlineStr">
         <is>
           <t>Exit - Rounded (K=1.0)</t>
         </is>
@@ -1752,7 +1972,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>6.8</v>
+        <v>3</v>
       </c>
       <c r="C7" s="4" t="n">
         <v>4</v>
@@ -2115,13 +2335,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -2155,175 +2375,216 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Tank</t>
+          <t>Fluido</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Tank 1</t>
+          <t>1 1
+366 103
+367 106 197 0 0 4 0 1 0
+368 0 2 10 Water 60 F 0 1</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Elevación</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>1 1
+366 103
+367 106 197 0 0 4 0 1 0
+368 0 2 10 Water 60 F 0 1</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Tank</t>
+          <t>Fluido</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>Tank 1</t>
+          <t>1 1
+366 103
+367 106 197 0 0 4 0 1 0
+368 0 2 10 Water 60 F 0 1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>Presión superficial</t>
+          <t>Temperatura</t>
         </is>
       </c>
       <c r="D3" s="4" t="n">
-        <v>94.5</v>
+        <v>25</v>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>kPa (abs)</t>
+          <t>°C</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>Tank</t>
+          <t>Fluido</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Tank 1</t>
+          <t>1 1
+366 103
+367 106 197 0 0 4 0 1 0
+368 0 2 10 Water 60 F 0 1</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Nivel de líquido</t>
+          <t>Densidad</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>0.6</v>
+        <v>997.05</v>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kg/m³</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Fluido</t>
+        </is>
+      </c>
+      <c r="B5" s="4" t="inlineStr">
+        <is>
+          <t>1 1
+366 103
+367 106 197 0 0 4 0 1 0
+368 0 2 10 Water 60 F 0 1</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>Viscosidad</t>
+        </is>
+      </c>
+      <c r="D5" s="4" t="n">
+        <v>0.8909</v>
+      </c>
+      <c r="E5" s="4" t="inlineStr">
+        <is>
+          <t>cP</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>Bomba Centrífuga</t>
+          <t>Fluido</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Centrifugal Pump 1</t>
+          <t>1 1
+366 103
+367 106 197 0 0 4 0 1 0
+368 0 2 10 Water 60 F 0 1</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Modo operación</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>flow</t>
-        </is>
+          <t>Viscosidad</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.000891</v>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pa·s</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>Bomba Centrífuga</t>
+          <t>Fluido</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>Centrifugal Pump 1</t>
+          <t>1 1
+366 103
+367 106 197 0 0 4 0 1 0
+368 0 2 10 Water 60 F 0 1</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>Caudal</t>
-        </is>
-      </c>
-      <c r="D7" s="4" t="n">
-        <v>96</v>
-      </c>
-      <c r="E7" s="4" t="inlineStr">
-        <is>
-          <t>m3/h</t>
-        </is>
-      </c>
+          <t>Modelo</t>
+        </is>
+      </c>
+      <c r="D7" s="4" t="inlineStr">
+        <is>
+          <t>NIST fluid model</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>Bomba Centrífuga</t>
+          <t>Fluido</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Centrifugal Pump 1</t>
+          <t>1 1
+366 103
+367 106 197 0 0 4 0 1 0
+368 0 2 10 Water 60 F 0 1</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Elev. succión</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>WATER.FLD</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>Tank</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Tank 1</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>Elevación</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
         <v>0.3</v>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>m</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="4" t="inlineStr">
-        <is>
-          <t>Bomba Centrífuga</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="inlineStr">
-        <is>
-          <t>Centrifugal Pump 1</t>
-        </is>
-      </c>
-      <c r="C9" s="4" t="inlineStr">
-        <is>
-          <t>Elev. descarga</t>
-        </is>
-      </c>
-      <c r="D9" s="4" t="n">
-        <v>4.424</v>
-      </c>
-      <c r="E9" s="4" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>m</t>
         </is>
@@ -2332,46 +2593,46 @@
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
         <is>
-          <t>Fixed dP Device</t>
+          <t>Tank</t>
         </is>
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>Fixed dP Device 1</t>
+          <t>Tank 1</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Elev. entrada</t>
+          <t>Presión superficial</t>
         </is>
       </c>
       <c r="D11" s="4" t="n">
-        <v>4.724</v>
+        <v>94.5</v>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>kPa (abs)</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Fixed dP Device</t>
+          <t>Tank</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Fixed dP Device 1</t>
+          <t>Tank 1</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Elev. salida</t>
+          <t>Nivel de líquido</t>
         </is>
       </c>
       <c r="D12" s="2" t="n">
-        <v>4.724</v>
+        <v>0.6</v>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
@@ -2379,126 +2640,126 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Fixed dP Device</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>Fixed dP Device 1</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>Caída de presión</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>bar</t>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>Bomba</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Centrifugal Pump 1</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Modo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>flow</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>Válvula de Control</t>
+          <t>Bomba</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Control Valve 1</t>
+          <t>Centrifugal Pump 1</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Elevación</t>
+          <t>Caudal</t>
         </is>
       </c>
       <c r="D15" s="4" t="n">
-        <v>7.5</v>
+        <v>96</v>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>m3/h</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Válvula de Control</t>
+          <t>Bomba</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Control Valve 1</t>
+          <t>Centrifugal Pump 1</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Modo operación</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Fixed Cv</t>
-        </is>
+          <t>Elev. succión</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.3</v>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
         <is>
-          <t>Válvula de Control</t>
+          <t>Bomba</t>
         </is>
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Control Valve 1</t>
+          <t>Centrifugal Pump 1</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Coef. de flujo</t>
+          <t>Elev. descarga</t>
         </is>
       </c>
       <c r="D17" s="4" t="n">
-        <v>150</v>
+        <v>4.424</v>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Cv</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
         <is>
-          <t>Pressure Boundary</t>
+          <t>Fixed dP</t>
         </is>
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Pressure Boundary 1</t>
+          <t>Fixed dP Device 1</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Elevación</t>
+          <t>Elev. entrada</t>
         </is>
       </c>
       <c r="D19" s="4" t="n">
-        <v>6</v>
+        <v>4.724</v>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
@@ -2509,52 +2770,177 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>Pressure Boundary</t>
+          <t>Fixed dP</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>Pressure Boundary 1</t>
+          <t>Fixed dP Device 1</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Presión</t>
+          <t>Elev. salida</t>
         </is>
       </c>
       <c r="D20" s="2" t="n">
-        <v>94.5</v>
+        <v>4.724</v>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>kPa (abs)</t>
+          <t>m</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="4" t="inlineStr">
         <is>
-          <t>Pressure Boundary</t>
+          <t>Fixed dP</t>
         </is>
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
+          <t>Fixed dP Device 1</t>
+        </is>
+      </c>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>ΔP</t>
+        </is>
+      </c>
+      <c r="D21" s="4" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="E21" s="4" t="inlineStr">
+        <is>
+          <t>bar</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>C. Valve</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="inlineStr">
+        <is>
+          <t>Control Valve 1</t>
+        </is>
+      </c>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>Elevación</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>C. Valve</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Control Valve 1</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Modo</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Fixed Cv</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>C. Valve</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>Control Valve 1</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Coef. flujo</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="n">
+        <v>150</v>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>Cv</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="inlineStr">
+        <is>
           <t>Pressure Boundary 1</t>
         </is>
       </c>
-      <c r="C21" s="4" t="inlineStr">
-        <is>
-          <t>Modo</t>
-        </is>
-      </c>
-      <c r="D21" s="4" t="inlineStr">
-        <is>
-          <t>pressure</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Elevación</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="n">
+        <v>6</v>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>PB</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Pressure Boundary 1</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Presión</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>94.5</v>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>kPa (abs)</t>
         </is>
       </c>
     </row>
